--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-19 17:35:19 UTC</t>
+    <t>2026-07-19 17:57:11 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>1</t>
+    <t>2</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>

--- a/security-reports/findings.xlsx
+++ b/security-reports/findings.xlsx
@@ -217,13 +217,13 @@
     <t>Assessment Date</t>
   </si>
   <si>
-    <t>2026-07-19 17:57:11 UTC</t>
+    <t>2026-07-19 18:22:05 UTC</t>
   </si>
   <si>
     <t>Build Number</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>Total Security Rules Checked</t>
